--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703577.7214834306</v>
+        <v>703578</v>
       </c>
       <c r="R2" t="n">
-        <v>6668668.356771124</v>
+        <v>6668668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2000-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98939</v>
+        <v>98940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98940</v>
+        <v>98941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98941</v>
+        <v>98944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98944</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69560123</v>
       </c>
       <c r="B2" t="n">
-        <v>98958</v>
+        <v>98960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69560123</v>
+        <v>6756391</v>
       </c>
       <c r="B2" t="n">
-        <v>98960</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,17 +703,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>200 m SV om Lappsjöns sydostspets, östra vägkanten, Upl</t>
+          <t>ARKIV// Korrnäs, 200 m SV om Lappsjön (*gk* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703578</v>
+        <v>703515</v>
       </c>
       <c r="R2" t="n">
-        <v>6668668</v>
+        <v>6668733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -738,19 +747,19 @@
           <t>Häverö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-AB-Nor-0337</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2005-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter. 18 plantor</t>
+          <t>2005-05-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,17 +774,335 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>AB-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69560123</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>504</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>200 m SV om Lappsjöns sydostspets, östra vägkanten, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>703578</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6668668</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2000-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. 18 plantor</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Ebbe Zachrisson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113682794</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Masugnsån, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703507</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668744</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113682795</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Masugnsån, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>703508</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668743</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 19829-2022 artfynd.xlsx
+++ b/artfynd/A 19829-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6756391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69560123</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>